--- a/artfynd/A 43711-2025 artfynd.xlsx
+++ b/artfynd/A 43711-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137320756</v>
       </c>
       <c r="B2" t="n">
-        <v>97515</v>
+        <v>97520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137320755</v>
       </c>
       <c r="B3" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137320757</v>
       </c>
       <c r="B4" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137320758</v>
       </c>
       <c r="B5" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>137320759</v>
       </c>
       <c r="B6" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43711-2025 artfynd.xlsx
+++ b/artfynd/A 43711-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137320756</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>97522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137320757</v>
       </c>
       <c r="B4" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137320758</v>
       </c>
       <c r="B5" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43711-2025 artfynd.xlsx
+++ b/artfynd/A 43711-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137320756</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>97528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>137320755</v>
       </c>
       <c r="B3" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -908,7 +908,7 @@
         <v>137320757</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         <v>137320758</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
         <v>137320759</v>
       </c>
       <c r="B6" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 43711-2025 artfynd.xlsx
+++ b/artfynd/A 43711-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137320756</v>
       </c>
       <c r="B2" t="n">
-        <v>97528</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137320757</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137320758</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>137320759</v>
       </c>
       <c r="B6" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43711-2025 artfynd.xlsx
+++ b/artfynd/A 43711-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137320756</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137320757</v>
       </c>
       <c r="B4" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137320758</v>
       </c>
       <c r="B5" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>137320759</v>
       </c>
       <c r="B6" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43711-2025 artfynd.xlsx
+++ b/artfynd/A 43711-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137320756</v>
       </c>
       <c r="B2" t="n">
-        <v>97541</v>
+        <v>97544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137320755</v>
+        <v>137377200</v>
       </c>
       <c r="B3" t="n">
-        <v>58196</v>
+        <v>78938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,35 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+          <t>Kvarnbo, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800858</v>
+        <v>800759</v>
       </c>
       <c r="R3" t="n">
-        <v>7328609</v>
+        <v>7328627</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,62 +887,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137320755</t>
+          <t>https://artportalen.se/Sighting/137377200</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137320757</v>
+        <v>137377199</v>
       </c>
       <c r="B4" t="n">
-        <v>99431</v>
+        <v>80544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+          <t>Kvarnbo, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800774</v>
+        <v>800764</v>
       </c>
       <c r="R4" t="n">
-        <v>7328780</v>
+        <v>7328667</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,62 +999,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137320757</t>
+          <t>https://artportalen.se/Sighting/137377199</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137320758</v>
+        <v>137377205</v>
       </c>
       <c r="B5" t="n">
-        <v>99431</v>
+        <v>80650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+          <t>Kvarnbo, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800787</v>
+        <v>800785</v>
       </c>
       <c r="R5" t="n">
-        <v>7328781</v>
+        <v>7328763</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Utblommade m frökapslar</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,62 +1111,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137320758</t>
+          <t>https://artportalen.se/Sighting/137377205</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137320759</v>
+        <v>137377196</v>
       </c>
       <c r="B6" t="n">
-        <v>79556</v>
+        <v>83524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>260591</v>
+        <v>6486</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+          <t>Kvarnbo, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800877</v>
+        <v>800806</v>
       </c>
       <c r="R6" t="n">
-        <v>7328845</v>
+        <v>7328580</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,18 +1223,1646 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137377196</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137377198</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>800766</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7328667</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377198</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137377202</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>800671</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7328642</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bohål I asp</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377202</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137377203</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>800719</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7328717</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377203</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137377206</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57221</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>800855</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7328813</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377206</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137377208</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57221</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>800864</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7328830</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 st uppflygande</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377208</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137320755</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>800858</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7328609</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137320755</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137377195</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>800821</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7328563</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera stycken</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377195</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137377204</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>800719</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7328715</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377204</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137320757</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99434</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>800774</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7328780</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137320757</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137320758</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99434</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>800787</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7328781</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Utblommade m frökapslar</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137320758</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137320759</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79558</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>800877</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7328845</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137320759</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137377197</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79558</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>800804</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7328590</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377197</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137377207</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79558</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>800862</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7328828</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377207</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137377209</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79558</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>800870</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7328836</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377209</t>
         </is>
       </c>
     </row>
@@ -1256,6 +2873,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43711-2025 artfynd.xlsx
+++ b/artfynd/A 43711-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137320756</v>
       </c>
       <c r="B2" t="n">
-        <v>97544</v>
+        <v>97548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137377200</v>
       </c>
       <c r="B3" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137377199</v>
       </c>
       <c r="B4" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137377205</v>
       </c>
       <c r="B5" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137377196</v>
       </c>
       <c r="B6" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137377198</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137377202</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>137377203</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137377206</v>
       </c>
       <c r="B10" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>137377208</v>
       </c>
       <c r="B11" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>137320755</v>
       </c>
       <c r="B12" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>137377195</v>
       </c>
       <c r="B13" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>137377204</v>
       </c>
       <c r="B14" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137320757</v>
       </c>
       <c r="B15" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>137320758</v>
       </c>
       <c r="B16" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137320759</v>
       </c>
       <c r="B17" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>137377197</v>
       </c>
       <c r="B18" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>137377207</v>
       </c>
       <c r="B19" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>137377209</v>
       </c>
       <c r="B20" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
